--- a/examples/HFP_kim+sam.xlsx
+++ b/examples/HFP_kim+sam.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,60 +432,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -495,16 +505,31 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -512,16 +537,31 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -529,16 +569,31 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -546,16 +601,31 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -563,16 +633,31 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -580,16 +665,31 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -597,16 +697,31 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -614,16 +729,31 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -631,16 +761,31 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -648,16 +793,31 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -665,16 +825,31 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -682,16 +857,31 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -699,16 +889,31 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -716,16 +921,31 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -733,16 +953,31 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -750,16 +985,31 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -767,16 +1017,31 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -784,16 +1049,31 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -801,16 +1081,31 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -818,16 +1113,31 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -835,16 +1145,31 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -852,16 +1177,31 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,16 +1209,31 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -886,16 +1241,31 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -903,16 +1273,31 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -920,16 +1305,31 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -937,16 +1337,31 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,16 +1369,31 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -971,16 +1401,31 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -988,16 +1433,31 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,16 +1465,31 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1022,16 +1497,31 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1039,16 +1529,31 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1056,16 +1561,31 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1073,16 +1593,31 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1090,16 +1625,31 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1107,16 +1657,31 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1131,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,60 +1712,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1210,16 +1785,31 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1227,16 +1817,31 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,16 +1849,31 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1261,16 +1881,31 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1278,16 +1913,31 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1295,16 +1945,31 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1312,16 +1977,31 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1329,16 +2009,31 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1346,16 +2041,31 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1363,16 +2073,31 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,16 +2105,31 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1397,16 +2137,31 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1414,16 +2169,31 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1431,16 +2201,31 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1448,16 +2233,31 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1465,16 +2265,31 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1482,16 +2297,31 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1499,16 +2329,31 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1516,16 +2361,31 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1533,16 +2393,31 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1550,16 +2425,31 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1567,16 +2457,31 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1584,16 +2489,31 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1601,16 +2521,31 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1618,16 +2553,31 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,16 +2585,31 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1652,16 +2617,31 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1669,16 +2649,31 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1686,16 +2681,31 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1703,16 +2713,31 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1720,16 +2745,31 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1737,16 +2777,31 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1754,16 +2809,31 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1771,16 +2841,31 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1788,16 +2873,31 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1805,16 +2905,31 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1822,16 +2937,31 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1848,10 +2978,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_kim+sam.xlsx
+++ b/examples/HFP_kim+sam.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,70 +432,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv fixed</t>
+          <t>big-ticket items</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>big-ticket items</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -505,31 +495,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -537,31 +512,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -569,31 +529,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,31 +546,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -633,31 +563,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -665,31 +580,16 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -697,31 +597,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -729,31 +614,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -761,31 +631,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -793,31 +648,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -825,31 +665,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -857,31 +682,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -889,31 +699,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -921,31 +716,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -953,31 +733,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -985,31 +750,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1017,31 +767,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1049,31 +784,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1081,31 +801,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1113,31 +818,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1145,31 +835,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1177,31 +852,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1209,31 +869,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1241,31 +886,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1273,31 +903,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1305,31 +920,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,31 +937,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1369,31 +954,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1401,31 +971,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1433,31 +988,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1465,31 +1005,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1497,31 +1022,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1529,31 +1039,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1561,31 +1056,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1593,31 +1073,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1625,31 +1090,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1657,31 +1107,16 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,70 +1147,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv fixed</t>
+          <t>big-ticket items</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>big-ticket items</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1785,31 +1210,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1817,31 +1227,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1849,31 +1244,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1881,31 +1261,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1913,31 +1278,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1945,31 +1295,16 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1977,31 +1312,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -2009,31 +1329,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -2041,31 +1346,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -2073,31 +1363,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2105,31 +1380,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2137,31 +1397,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2169,31 +1414,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2201,31 +1431,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2233,31 +1448,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2265,31 +1465,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2297,31 +1482,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2329,31 +1499,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2361,31 +1516,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,31 +1533,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2425,31 +1550,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2457,31 +1567,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2489,31 +1584,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2521,31 +1601,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2553,31 +1618,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2585,31 +1635,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2617,31 +1652,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2649,31 +1669,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2681,31 +1686,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2713,31 +1703,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2745,31 +1720,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2777,31 +1737,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2809,31 +1754,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2841,31 +1771,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2873,31 +1788,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2905,31 +1805,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2937,31 +1822,16 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2978,6 +1848,10 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
